--- a/example/example-0001_dra_metadata.xlsx
+++ b/example/example-0001_dra_metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\github\submission-excel2xml\example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\github\sub2xml-dra-1.6.1\submission-excel2xml\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F22A8E5-400A-4951-8CFC-ADD5E5DE04B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFA4B92-087B-43E8-9B13-FB3699CFD840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="9" r:id="rId1"/>
@@ -420,7 +420,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="264">
   <si>
     <t>Library Source</t>
   </si>
@@ -1233,11 +1233,15 @@
     <t>Sentosa SQ301</t>
   </si>
   <si>
-    <t>2024-10-23 Bioinformation and DDBJ Center</t>
+    <t>v3.2</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>v3.1</t>
+    <t>2025-xx-yy Bioinformation and DDBJ Center</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Illumina NovaSeq X Plus</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1719,12 +1723,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="52.8">
@@ -2038,7 +2042,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3D1F9A0B-2ADE-4FE8-91BF-DADC9BF0CB6A}">
           <x14:formula1>
-            <xm:f>Admin!$D$2:$D$82</xm:f>
+            <xm:f>Admin!$D$2:$D$83</xm:f>
           </x14:formula1>
           <xm:sqref>I2:I3000</xm:sqref>
         </x14:dataValidation>
@@ -28772,7 +28776,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="32.33203125" style="2" bestFit="1" customWidth="1"/>
@@ -29153,8 +29157,8 @@
       <c r="C19" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>63</v>
+      <c r="D19" s="2" t="s">
+        <v>263</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -29170,7 +29174,7 @@
         <v>55</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>153</v>
+        <v>63</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -29186,7 +29190,7 @@
         <v>57</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -29202,7 +29206,7 @@
         <v>59</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -29218,7 +29222,7 @@
         <v>4</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -29234,7 +29238,7 @@
         <v>67</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -29250,7 +29254,7 @@
         <v>70</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>247</v>
+        <v>155</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -29266,7 +29270,7 @@
         <v>73</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>156</v>
+        <v>247</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -29282,7 +29286,7 @@
         <v>75</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -29298,7 +29302,7 @@
         <v>78</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -29314,7 +29318,7 @@
         <v>146</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -29330,7 +29334,7 @@
         <v>81</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>248</v>
+        <v>158</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -29344,7 +29348,7 @@
         <v>83</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>90</v>
+        <v>248</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -29358,7 +29362,7 @@
         <v>150</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
@@ -29372,7 +29376,7 @@
         <v>85</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
@@ -29386,7 +29390,7 @@
         <v>87</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
@@ -29400,7 +29404,7 @@
         <v>111</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>249</v>
+        <v>159</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
@@ -29414,7 +29418,7 @@
         <v>110</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
@@ -29428,7 +29432,7 @@
         <v>147</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
@@ -29442,7 +29446,7 @@
         <v>38</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>88</v>
+        <v>251</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
@@ -29454,7 +29458,7 @@
       <c r="B39" s="6"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
@@ -29466,7 +29470,7 @@
       <c r="B40" s="6"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
@@ -29474,212 +29478,217 @@
       <c r="H40" s="5"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="D41" s="2" t="s">
-        <v>160</v>
+      <c r="D41" s="5" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="D42" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="D43" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="D44" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="D45" s="2" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="D45" s="5" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="D46" s="5" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="D47" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="D48" s="5" t="s">
         <v>123</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="D48" s="2" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="49" spans="4:4">
       <c r="D49" s="2" t="s">
-        <v>18</v>
+        <v>252</v>
       </c>
     </row>
     <row r="50" spans="4:4">
       <c r="D50" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="4:4">
       <c r="D51" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="4:4">
       <c r="D52" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="53" spans="4:4">
       <c r="D53" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="4:4">
       <c r="D54" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="4:4">
       <c r="D55" s="2" t="s">
-        <v>100</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56" spans="4:4">
       <c r="D56" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="4:4">
       <c r="D57" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="58" spans="4:4">
       <c r="D58" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="4:4">
       <c r="D59" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60" spans="4:4">
       <c r="D60" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="61" spans="4:4">
       <c r="D61" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62" spans="4:4">
       <c r="D62" s="2" t="s">
-        <v>253</v>
+        <v>94</v>
       </c>
     </row>
     <row r="63" spans="4:4">
       <c r="D63" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="64" spans="4:4">
       <c r="D64" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="65" spans="4:4">
       <c r="D65" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="66" spans="4:4">
       <c r="D66" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="67" spans="4:4">
       <c r="D67" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="68" spans="4:4">
       <c r="D68" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="69" spans="4:4">
       <c r="D69" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="70" spans="4:4">
       <c r="D70" s="2" t="s">
-        <v>68</v>
+        <v>260</v>
       </c>
     </row>
     <row r="71" spans="4:4">
       <c r="D71" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72" spans="4:4">
       <c r="D72" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="73" spans="4:4">
       <c r="D73" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="4:4">
       <c r="D74" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="4:4">
       <c r="D75" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="4:4">
       <c r="D76" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="77" spans="4:4">
       <c r="D77" s="2" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
     </row>
     <row r="78" spans="4:4">
       <c r="D78" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="79" spans="4:4">
       <c r="D79" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="80" spans="4:4">
       <c r="D80" s="2" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
     </row>
     <row r="81" spans="4:4">
       <c r="D81" s="2" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="82" spans="4:4">
       <c r="D82" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="83" spans="4:4">
+      <c r="D83" s="2" t="s">
         <v>80</v>
       </c>
     </row>

--- a/example/example-0001_dra_metadata.xlsx
+++ b/example/example-0001_dra_metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\github\submission-excel2xml\example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\github\submission-excel2xml-dra161\submission-excel2xml\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F22A8E5-400A-4951-8CFC-ADD5E5DE04B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12EA0240-497E-4123-B474-393C9F541F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="877" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="9" r:id="rId1"/>
@@ -420,7 +420,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="275">
   <si>
     <t>Library Source</t>
   </si>
@@ -1233,11 +1233,47 @@
     <t>Sentosa SQ301</t>
   </si>
   <si>
-    <t>2024-10-23 Bioinformation and DDBJ Center</t>
+    <t>Illumina MiSeq i100</t>
+  </si>
+  <si>
+    <t>Illumina MiSeq i100 Plus</t>
+  </si>
+  <si>
+    <t>Illumina NovaSeq X Plus</t>
+  </si>
+  <si>
+    <t>DNBSEQ-T1+</t>
+  </si>
+  <si>
+    <t>CycloneSEQ</t>
+  </si>
+  <si>
+    <t>SURFSeq 5000</t>
+  </si>
+  <si>
+    <t>SURFSeq Q</t>
+  </si>
+  <si>
+    <t>Saluseq Nimbo</t>
+  </si>
+  <si>
+    <t>Salus Pro</t>
+  </si>
+  <si>
+    <t>Salus EVO</t>
+  </si>
+  <si>
+    <t>G-seq500</t>
+  </si>
+  <si>
+    <t>G4</t>
+  </si>
+  <si>
+    <t>2026-02-24 Bioinformation and DDBJ Center</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>v3.1</t>
+    <t>v3.3</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1719,12 +1755,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="52.8">
@@ -1776,7 +1812,7 @@
         <v>242</v>
       </c>
       <c r="B2" s="1">
-        <v>46023</v>
+        <v>46753</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>244</v>
@@ -2038,7 +2074,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3D1F9A0B-2ADE-4FE8-91BF-DADC9BF0CB6A}">
           <x14:formula1>
-            <xm:f>Admin!$D$2:$D$82</xm:f>
+            <xm:f>Admin!$D$2:$D$94</xm:f>
           </x14:formula1>
           <xm:sqref>I2:I3000</xm:sqref>
         </x14:dataValidation>
@@ -28772,7 +28808,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="32.33203125" style="2" bestFit="1" customWidth="1"/>
@@ -29106,7 +29142,7 @@
         <v>45</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>163</v>
+        <v>261</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
@@ -29122,7 +29158,7 @@
         <v>48</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>114</v>
+        <v>262</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
@@ -29138,7 +29174,7 @@
         <v>51</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>246</v>
+        <v>163</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
@@ -29154,7 +29190,7 @@
         <v>54</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -29170,7 +29206,7 @@
         <v>55</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>153</v>
+        <v>246</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -29186,7 +29222,7 @@
         <v>57</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>151</v>
+        <v>263</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -29202,7 +29238,7 @@
         <v>59</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>152</v>
+        <v>63</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -29218,7 +29254,7 @@
         <v>4</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -29234,7 +29270,7 @@
         <v>67</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -29250,7 +29286,7 @@
         <v>70</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>247</v>
+        <v>152</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -29266,7 +29302,7 @@
         <v>73</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -29282,7 +29318,7 @@
         <v>75</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -29298,7 +29334,7 @@
         <v>78</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>154</v>
+        <v>247</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -29314,7 +29350,7 @@
         <v>146</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -29330,7 +29366,7 @@
         <v>81</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>248</v>
+        <v>157</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -29344,7 +29380,7 @@
         <v>83</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>90</v>
+        <v>264</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -29358,7 +29394,7 @@
         <v>150</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>91</v>
+        <v>154</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
@@ -29372,7 +29408,7 @@
         <v>85</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
@@ -29386,7 +29422,7 @@
         <v>87</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>159</v>
+        <v>248</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
@@ -29400,7 +29436,7 @@
         <v>111</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
@@ -29414,7 +29450,7 @@
         <v>110</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>250</v>
+        <v>90</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
@@ -29428,7 +29464,7 @@
         <v>147</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>251</v>
+        <v>91</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
@@ -29442,7 +29478,7 @@
         <v>38</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
@@ -29454,7 +29490,7 @@
       <c r="B39" s="6"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5" t="s">
-        <v>89</v>
+        <v>159</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
@@ -29466,7 +29502,7 @@
       <c r="B40" s="6"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5" t="s">
-        <v>120</v>
+        <v>249</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
@@ -29475,211 +29511,271 @@
     </row>
     <row r="41" spans="1:8">
       <c r="D41" s="2" t="s">
-        <v>160</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="D42" s="2" t="s">
-        <v>161</v>
+        <v>251</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="D43" s="2" t="s">
-        <v>162</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="D44" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="D45" s="5" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="D46" s="5" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="D47" s="5" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="D48" s="2" t="s">
-        <v>252</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49" spans="4:4">
       <c r="D49" s="2" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50" spans="4:4">
       <c r="D50" s="2" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="4:4">
       <c r="D51" s="2" t="s">
-        <v>27</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="4:4">
       <c r="D52" s="2" t="s">
-        <v>31</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53" spans="4:4">
       <c r="D53" s="2" t="s">
-        <v>35</v>
+        <v>252</v>
       </c>
     </row>
     <row r="54" spans="4:4">
       <c r="D54" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55" spans="4:4">
       <c r="D55" s="2" t="s">
-        <v>100</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="4:4">
       <c r="D56" s="2" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="4:4">
       <c r="D57" s="2" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="4:4">
       <c r="D58" s="2" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="4:4">
       <c r="D59" s="2" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60" spans="4:4">
       <c r="D60" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61" spans="4:4">
       <c r="D61" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62" spans="4:4">
       <c r="D62" s="2" t="s">
-        <v>253</v>
+        <v>98</v>
       </c>
     </row>
     <row r="63" spans="4:4">
       <c r="D63" s="2" t="s">
-        <v>254</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="4:4">
       <c r="D64" s="2" t="s">
-        <v>255</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" spans="4:4">
       <c r="D65" s="2" t="s">
-        <v>256</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="4:4">
       <c r="D66" s="2" t="s">
-        <v>257</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="4:4">
       <c r="D67" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="68" spans="4:4">
       <c r="D68" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="69" spans="4:4">
       <c r="D69" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="70" spans="4:4">
       <c r="D70" s="2" t="s">
-        <v>68</v>
+        <v>266</v>
       </c>
     </row>
     <row r="71" spans="4:4">
       <c r="D71" s="2" t="s">
-        <v>71</v>
+        <v>267</v>
       </c>
     </row>
     <row r="72" spans="4:4">
       <c r="D72" s="2" t="s">
-        <v>74</v>
+        <v>256</v>
       </c>
     </row>
     <row r="73" spans="4:4">
       <c r="D73" s="2" t="s">
-        <v>76</v>
+        <v>257</v>
       </c>
     </row>
     <row r="74" spans="4:4">
       <c r="D74" s="2" t="s">
-        <v>79</v>
+        <v>258</v>
       </c>
     </row>
     <row r="75" spans="4:4">
       <c r="D75" s="2" t="s">
-        <v>82</v>
+        <v>259</v>
       </c>
     </row>
     <row r="76" spans="4:4">
       <c r="D76" s="2" t="s">
-        <v>84</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" spans="4:4">
       <c r="D77" s="2" t="s">
-        <v>117</v>
+        <v>268</v>
       </c>
     </row>
     <row r="78" spans="4:4">
       <c r="D78" s="2" t="s">
-        <v>118</v>
+        <v>269</v>
       </c>
     </row>
     <row r="79" spans="4:4">
       <c r="D79" s="2" t="s">
-        <v>119</v>
+        <v>270</v>
       </c>
     </row>
     <row r="80" spans="4:4">
       <c r="D80" s="2" t="s">
-        <v>65</v>
+        <v>271</v>
       </c>
     </row>
     <row r="81" spans="4:4">
       <c r="D81" s="2" t="s">
-        <v>86</v>
+        <v>272</v>
       </c>
     </row>
     <row r="82" spans="4:4">
       <c r="D82" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="83" spans="4:4">
+      <c r="D83" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="84" spans="4:4">
+      <c r="D84" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" spans="4:4">
+      <c r="D85" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="86" spans="4:4">
+      <c r="D86" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="87" spans="4:4">
+      <c r="D87" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="88" spans="4:4">
+      <c r="D88" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="89" spans="4:4">
+      <c r="D89" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="90" spans="4:4">
+      <c r="D90" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="91" spans="4:4">
+      <c r="D91" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="92" spans="4:4">
+      <c r="D92" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="93" spans="4:4">
+      <c r="D93" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="94" spans="4:4">
+      <c r="D94" s="2" t="s">
         <v>80</v>
       </c>
     </row>
